--- a/grupos/2ARHM - Estadisticos 20232.xlsx
+++ b/grupos/2ARHM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="169">
   <si>
     <t>Materia</t>
   </si>
@@ -212,25 +212,25 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Sanchez Morales Gilberto</t>
+  </si>
+  <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
     <t>NC</t>
@@ -1092,28 +1092,28 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -1146,7 +1146,7 @@
         <v>-1</v>
       </c>
       <c r="AD4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE4">
         <v>10</v>
@@ -1164,7 +1164,7 @@
         <v>10</v>
       </c>
       <c r="AJ4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK4">
         <v>-1</v>
@@ -1205,28 +1205,28 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1262,10 +1262,10 @@
         <v>5</v>
       </c>
       <c r="AE5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG5">
         <v>8</v>
@@ -1274,10 +1274,10 @@
         <v>6</v>
       </c>
       <c r="AI5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK5">
         <v>-1</v>
@@ -1318,28 +1318,28 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1372,22 +1372,22 @@
         <v>-1</v>
       </c>
       <c r="AD6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE6">
         <v>7</v>
       </c>
       <c r="AF6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH6">
         <v>10</v>
       </c>
       <c r="AI6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ6">
         <v>7</v>
@@ -1431,28 +1431,28 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1488,13 +1488,13 @@
         <v>5</v>
       </c>
       <c r="AE7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH7">
         <v>5</v>
@@ -1544,28 +1544,28 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1604,10 +1604,10 @@
         <v>5</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH8">
         <v>6</v>
@@ -1657,28 +1657,28 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1711,22 +1711,22 @@
         <v>-1</v>
       </c>
       <c r="AD9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE9">
         <v>5</v>
       </c>
       <c r="AF9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH9">
         <v>6</v>
       </c>
       <c r="AI9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ9">
         <v>5</v>
@@ -1770,28 +1770,28 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1824,7 +1824,7 @@
         <v>-1</v>
       </c>
       <c r="AD10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE10">
         <v>10</v>
@@ -1883,28 +1883,28 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1943,16 +1943,16 @@
         <v>9</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH11">
         <v>9</v>
       </c>
       <c r="AI11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ11">
         <v>6</v>
@@ -1996,28 +1996,28 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -2050,13 +2050,13 @@
         <v>-1</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE12">
         <v>8</v>
       </c>
       <c r="AF12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -2065,7 +2065,7 @@
         <v>10</v>
       </c>
       <c r="AI12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ12">
         <v>7</v>
@@ -2109,28 +2109,28 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -2163,7 +2163,7 @@
         <v>-1</v>
       </c>
       <c r="AD13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE13">
         <v>8</v>
@@ -2181,7 +2181,7 @@
         <v>10</v>
       </c>
       <c r="AJ13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK13">
         <v>-1</v>
@@ -2222,28 +2222,28 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -2276,22 +2276,22 @@
         <v>-1</v>
       </c>
       <c r="AD14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE14">
         <v>6</v>
       </c>
       <c r="AF14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH14">
         <v>7</v>
       </c>
       <c r="AI14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ14">
         <v>6</v>
@@ -2335,28 +2335,28 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -2389,11 +2389,11 @@
         <v>-1</v>
       </c>
       <c r="AD15">
+        <v>8</v>
+      </c>
+      <c r="AE15">
         <v>7</v>
       </c>
-      <c r="AE15">
-        <v>6</v>
-      </c>
       <c r="AF15">
         <v>10</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>10</v>
       </c>
       <c r="AJ15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK15">
         <v>-1</v>
@@ -2448,28 +2448,28 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2508,7 +2508,7 @@
         <v>5</v>
       </c>
       <c r="AF16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG16">
         <v>5</v>
@@ -2561,28 +2561,28 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2621,16 +2621,16 @@
         <v>6</v>
       </c>
       <c r="AF17">
+        <v>7</v>
+      </c>
+      <c r="AG17">
         <v>8</v>
       </c>
-      <c r="AG17">
+      <c r="AH17">
+        <v>6</v>
+      </c>
+      <c r="AI17">
         <v>7</v>
-      </c>
-      <c r="AH17">
-        <v>6</v>
-      </c>
-      <c r="AI17">
-        <v>5</v>
       </c>
       <c r="AJ17">
         <v>5</v>
@@ -2674,28 +2674,28 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2728,25 +2728,25 @@
         <v>-1</v>
       </c>
       <c r="AD18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE18">
         <v>9</v>
       </c>
       <c r="AF18">
+        <v>9</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+      <c r="AH18">
+        <v>9</v>
+      </c>
+      <c r="AI18">
+        <v>10</v>
+      </c>
+      <c r="AJ18">
         <v>8</v>
-      </c>
-      <c r="AG18">
-        <v>10</v>
-      </c>
-      <c r="AH18">
-        <v>9</v>
-      </c>
-      <c r="AI18">
-        <v>10</v>
-      </c>
-      <c r="AJ18">
-        <v>7</v>
       </c>
       <c r="AK18">
         <v>-1</v>
@@ -2787,28 +2787,28 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2856,10 +2856,10 @@
         <v>9</v>
       </c>
       <c r="AI19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK19">
         <v>-1</v>
@@ -2900,28 +2900,28 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2954,22 +2954,22 @@
         <v>-1</v>
       </c>
       <c r="AD20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE20">
         <v>5</v>
       </c>
       <c r="AF20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH20">
         <v>8</v>
       </c>
       <c r="AI20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ20">
         <v>7</v>
@@ -3013,28 +3013,28 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -3073,10 +3073,10 @@
         <v>5</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH21">
         <v>5</v>
@@ -3126,28 +3126,28 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -3180,22 +3180,22 @@
         <v>-1</v>
       </c>
       <c r="AD22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH22">
         <v>9</v>
       </c>
       <c r="AI22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ22">
         <v>8</v>
@@ -3239,28 +3239,28 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -3293,7 +3293,7 @@
         <v>-1</v>
       </c>
       <c r="AD23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE23">
         <v>7</v>
@@ -3308,10 +3308,10 @@
         <v>9</v>
       </c>
       <c r="AI23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK23">
         <v>-1</v>
@@ -3352,28 +3352,28 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -3406,7 +3406,7 @@
         <v>-1</v>
       </c>
       <c r="AD24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE24">
         <v>8</v>
@@ -3424,7 +3424,7 @@
         <v>10</v>
       </c>
       <c r="AJ24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK24">
         <v>-1</v>
@@ -3465,28 +3465,28 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -3522,10 +3522,10 @@
         <v>5</v>
       </c>
       <c r="AE25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG25">
         <v>8</v>
@@ -3534,7 +3534,7 @@
         <v>6</v>
       </c>
       <c r="AI25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ25">
         <v>6</v>
@@ -3578,28 +3578,28 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -3691,28 +3691,28 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3748,10 +3748,10 @@
         <v>5</v>
       </c>
       <c r="AE27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG27">
         <v>6</v>
@@ -3760,10 +3760,10 @@
         <v>6</v>
       </c>
       <c r="AI27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK27">
         <v>-1</v>
@@ -3804,28 +3804,28 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3864,7 +3864,7 @@
         <v>7</v>
       </c>
       <c r="AF28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG28">
         <v>9</v>
@@ -3873,7 +3873,7 @@
         <v>9</v>
       </c>
       <c r="AI28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ28">
         <v>6</v>
@@ -3917,28 +3917,28 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3971,7 +3971,7 @@
         <v>-1</v>
       </c>
       <c r="AD29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE29">
         <v>6</v>
@@ -3980,16 +3980,16 @@
         <v>10</v>
       </c>
       <c r="AG29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH29">
         <v>8</v>
       </c>
       <c r="AI29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK29">
         <v>-1</v>
@@ -4030,28 +4030,28 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -4084,25 +4084,25 @@
         <v>-1</v>
       </c>
       <c r="AD30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE30">
+        <v>8</v>
+      </c>
+      <c r="AF30">
+        <v>9</v>
+      </c>
+      <c r="AG30">
+        <v>9</v>
+      </c>
+      <c r="AH30">
+        <v>10</v>
+      </c>
+      <c r="AI30">
+        <v>10</v>
+      </c>
+      <c r="AJ30">
         <v>7</v>
-      </c>
-      <c r="AF30">
-        <v>8</v>
-      </c>
-      <c r="AG30">
-        <v>8</v>
-      </c>
-      <c r="AH30">
-        <v>10</v>
-      </c>
-      <c r="AI30">
-        <v>9</v>
-      </c>
-      <c r="AJ30">
-        <v>6</v>
       </c>
       <c r="AK30">
         <v>-1</v>
@@ -4143,28 +4143,28 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>-1</v>
@@ -4200,10 +4200,10 @@
         <v>8</v>
       </c>
       <c r="AE31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -4212,10 +4212,10 @@
         <v>10</v>
       </c>
       <c r="AI31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK31">
         <v>-1</v>
@@ -4256,28 +4256,28 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -4310,7 +4310,7 @@
         <v>-1</v>
       </c>
       <c r="AD32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE32">
         <v>9</v>
@@ -4369,28 +4369,28 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>-1</v>
@@ -4423,7 +4423,7 @@
         <v>-1</v>
       </c>
       <c r="AD33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE33">
         <v>10</v>
@@ -4438,7 +4438,7 @@
         <v>10</v>
       </c>
       <c r="AI33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ33">
         <v>8</v>
@@ -4482,28 +4482,28 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>-1</v>
@@ -4539,22 +4539,22 @@
         <v>5</v>
       </c>
       <c r="AE34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH34">
         <v>7</v>
       </c>
       <c r="AI34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK34">
         <v>-1</v>
@@ -4595,28 +4595,28 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>-1</v>
@@ -4652,10 +4652,10 @@
         <v>5</v>
       </c>
       <c r="AE35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG35">
         <v>6</v>
@@ -4664,7 +4664,7 @@
         <v>7</v>
       </c>
       <c r="AI35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ35">
         <v>5</v>
@@ -4708,28 +4708,28 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>-1</v>
@@ -4768,10 +4768,10 @@
         <v>5</v>
       </c>
       <c r="AF36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH36">
         <v>6</v>
@@ -4780,7 +4780,7 @@
         <v>5</v>
       </c>
       <c r="AJ36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK36">
         <v>-1</v>
@@ -4821,28 +4821,28 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>-1</v>
@@ -4875,25 +4875,25 @@
         <v>-1</v>
       </c>
       <c r="AD37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE37">
+        <v>9</v>
+      </c>
+      <c r="AF37">
+        <v>10</v>
+      </c>
+      <c r="AG37">
+        <v>10</v>
+      </c>
+      <c r="AH37">
+        <v>9</v>
+      </c>
+      <c r="AI37">
+        <v>10</v>
+      </c>
+      <c r="AJ37">
         <v>8</v>
-      </c>
-      <c r="AF37">
-        <v>10</v>
-      </c>
-      <c r="AG37">
-        <v>9</v>
-      </c>
-      <c r="AH37">
-        <v>9</v>
-      </c>
-      <c r="AI37">
-        <v>10</v>
-      </c>
-      <c r="AJ37">
-        <v>7</v>
       </c>
       <c r="AK37">
         <v>-1</v>
@@ -4934,28 +4934,28 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>-1</v>
@@ -5279,10 +5279,10 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>89.5</v>
+        <v>90.7</v>
       </c>
       <c r="M5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N5">
         <v>100</v>
@@ -5297,7 +5297,7 @@
         <v>93.8</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -5306,10 +5306,10 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>89.5</v>
+        <v>90.7</v>
       </c>
       <c r="V5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="W5">
         <v>100</v>
@@ -5324,7 +5324,7 @@
         <v>93.8</v>
       </c>
       <c r="AA5">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="AB5">
         <v>100</v>
@@ -5365,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -5380,7 +5380,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -5407,7 +5407,7 @@
         <v>100</v>
       </c>
       <c r="Z6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA6">
         <v>100</v>
@@ -5451,25 +5451,25 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>84.2</v>
+        <v>46.5</v>
       </c>
       <c r="M7">
         <v>80</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="P7">
         <v>73.3</v>
       </c>
       <c r="Q7">
-        <v>75</v>
+        <v>40.6</v>
       </c>
       <c r="R7">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -5478,25 +5478,25 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>84.2</v>
+        <v>46.5</v>
       </c>
       <c r="V7">
         <v>80</v>
       </c>
       <c r="W7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="X7">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="Y7">
         <v>73.3</v>
       </c>
       <c r="Z7">
-        <v>75</v>
+        <v>40.6</v>
       </c>
       <c r="AA7">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AB7">
         <v>100</v>
@@ -5537,25 +5537,25 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>84.2</v>
+        <v>46.5</v>
       </c>
       <c r="M8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="P8">
         <v>86.7</v>
       </c>
       <c r="Q8">
-        <v>87.5</v>
+        <v>43.8</v>
       </c>
       <c r="R8">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -5564,25 +5564,25 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>84.2</v>
+        <v>46.5</v>
       </c>
       <c r="V8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="W8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="X8">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="Y8">
         <v>86.7</v>
       </c>
       <c r="Z8">
-        <v>87.5</v>
+        <v>43.8</v>
       </c>
       <c r="AA8">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AB8">
         <v>100</v>
@@ -5623,13 +5623,13 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>89.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -5638,25 +5638,25 @@
         <v>93.3</v>
       </c>
       <c r="Q9">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="R9">
+        <v>87.5</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="V9">
         <v>90</v>
       </c>
-      <c r="S9">
-        <v>100</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>89.5</v>
-      </c>
-      <c r="V9">
-        <v>100</v>
-      </c>
       <c r="W9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="X9">
         <v>100</v>
@@ -5665,10 +5665,10 @@
         <v>93.3</v>
       </c>
       <c r="Z9">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="AA9">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="AB9">
         <v>100</v>
@@ -5985,7 +5985,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -6012,7 +6012,7 @@
         <v>100</v>
       </c>
       <c r="AA13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB13">
         <v>100</v>
@@ -6059,7 +6059,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -6068,10 +6068,10 @@
         <v>80</v>
       </c>
       <c r="Q14">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R14">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -6086,7 +6086,7 @@
         <v>100</v>
       </c>
       <c r="W14">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="X14">
         <v>100</v>
@@ -6095,10 +6095,10 @@
         <v>80</v>
       </c>
       <c r="Z14">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AA14">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="AB14">
         <v>100</v>
@@ -6225,25 +6225,25 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>89.5</v>
+        <v>62.8</v>
       </c>
       <c r="M16">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N16">
         <v>92</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P16">
         <v>86.7</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -6252,25 +6252,25 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>89.5</v>
+        <v>62.8</v>
       </c>
       <c r="V16">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="W16">
         <v>92</v>
       </c>
       <c r="X16">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y16">
         <v>86.7</v>
       </c>
       <c r="Z16">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="AA16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB16">
         <v>100</v>
@@ -6311,10 +6311,10 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>89.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N17">
         <v>100</v>
@@ -6329,7 +6329,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -6338,10 +6338,10 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>89.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="W17">
         <v>100</v>
@@ -6356,7 +6356,7 @@
         <v>100</v>
       </c>
       <c r="AA17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB17">
         <v>100</v>
@@ -6412,7 +6412,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -6439,7 +6439,7 @@
         <v>100</v>
       </c>
       <c r="Z18">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA18">
         <v>100</v>
@@ -6498,7 +6498,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -6525,7 +6525,7 @@
         <v>100</v>
       </c>
       <c r="Z19">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA19">
         <v>100</v>
@@ -6569,7 +6569,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>84.2</v>
+        <v>93</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -6584,7 +6584,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -6596,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>84.2</v>
+        <v>93</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -6611,7 +6611,7 @@
         <v>100</v>
       </c>
       <c r="Z20">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA20">
         <v>100</v>
@@ -6628,7 +6628,7 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="D21">
         <v>60</v>
@@ -6655,25 +6655,25 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>60.5</v>
       </c>
       <c r="M21">
         <v>60</v>
       </c>
       <c r="N21">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P21">
         <v>66.7</v>
       </c>
       <c r="Q21">
-        <v>62.5</v>
+        <v>43.8</v>
       </c>
       <c r="R21">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -6682,25 +6682,25 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>60.5</v>
       </c>
       <c r="V21">
         <v>60</v>
       </c>
       <c r="W21">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="X21">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y21">
         <v>66.7</v>
       </c>
       <c r="Z21">
-        <v>62.5</v>
+        <v>43.8</v>
       </c>
       <c r="AA21">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="AB21">
         <v>100</v>
@@ -6747,7 +6747,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -6756,10 +6756,10 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R22">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -6774,7 +6774,7 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X22">
         <v>100</v>
@@ -6783,10 +6783,10 @@
         <v>100</v>
       </c>
       <c r="Z22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA22">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="AB22">
         <v>100</v>
@@ -6833,7 +6833,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -6860,7 +6860,7 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="X23">
         <v>100</v>
@@ -7002,10 +7002,10 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -7014,7 +7014,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -7029,10 +7029,10 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="W25">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X25">
         <v>100</v>
@@ -7041,7 +7041,7 @@
         <v>100</v>
       </c>
       <c r="Z25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AA25">
         <v>100</v>
@@ -7088,10 +7088,10 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N26">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -7103,7 +7103,7 @@
         <v>93.8</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -7115,10 +7115,10 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="W26">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -7130,7 +7130,7 @@
         <v>93.8</v>
       </c>
       <c r="AA26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB26">
         <v>100</v>
@@ -7171,13 +7171,13 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="M27">
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -7186,10 +7186,10 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -7198,13 +7198,13 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="V27">
         <v>100</v>
       </c>
       <c r="W27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X27">
         <v>100</v>
@@ -7213,10 +7213,10 @@
         <v>100</v>
       </c>
       <c r="Z27">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="AA27">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="AB27">
         <v>100</v>
@@ -7533,7 +7533,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -7560,7 +7560,7 @@
         <v>100</v>
       </c>
       <c r="AA31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AB31">
         <v>100</v>
@@ -7773,13 +7773,13 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>84.2</v>
+        <v>93</v>
       </c>
       <c r="M34">
         <v>80</v>
       </c>
       <c r="N34">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -7791,7 +7791,7 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -7800,13 +7800,13 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>84.2</v>
+        <v>93</v>
       </c>
       <c r="V34">
         <v>80</v>
       </c>
       <c r="W34">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X34">
         <v>100</v>
@@ -7818,7 +7818,7 @@
         <v>100</v>
       </c>
       <c r="AA34">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="AB34">
         <v>100</v>
@@ -7832,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -7859,10 +7859,10 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>60.5</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N35">
         <v>100</v>
@@ -7874,10 +7874,10 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="R35">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -7886,10 +7886,10 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>60.5</v>
       </c>
       <c r="V35">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="W35">
         <v>100</v>
@@ -7901,10 +7901,10 @@
         <v>100</v>
       </c>
       <c r="Z35">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="AA35">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB35">
         <v>100</v>
@@ -7918,7 +7918,7 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="D36">
         <v>80</v>
@@ -7945,13 +7945,13 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="M36">
         <v>80</v>
       </c>
       <c r="N36">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O36">
         <v>100</v>
@@ -7963,7 +7963,7 @@
         <v>87.5</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="V36">
         <v>80</v>
       </c>
       <c r="W36">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="X36">
         <v>100</v>
@@ -7990,7 +7990,7 @@
         <v>87.5</v>
       </c>
       <c r="AA36">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="AB36">
         <v>100</v>
@@ -8280,7 +8280,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -8289,19 +8289,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2">
-        <v>57.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>42.9</v>
+        <v>31.4</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -8321,19 +8321,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2">
-        <v>77.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>22.9</v>
+        <v>31.4</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8353,19 +8353,19 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2">
-        <v>77.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>22.9</v>
+        <v>31.4</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8376,7 +8376,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -8385,19 +8385,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>82.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="G7" s="2">
-        <v>17.1</v>
+        <v>20</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8408,7 +8408,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
@@ -8417,19 +8417,19 @@
         <v>35</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>91.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G8" s="2">
-        <v>8.6</v>
+        <v>14.3</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8440,7 +8440,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
@@ -8449,19 +8449,19 @@
         <v>35</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>94.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="H9">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -8472,7 +8472,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
@@ -8481,19 +8481,19 @@
         <v>35</v>
       </c>
       <c r="D10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G10" s="2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="H10">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -9243,7 +9243,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9551,16 +9551,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920058</v>
+        <v>23330051920057</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -9574,16 +9574,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920058</v>
+        <v>23330051920057</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
@@ -9597,16 +9597,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920060</v>
+        <v>23330051920058</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -9620,16 +9620,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920060</v>
+        <v>23330051920058</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
@@ -9643,16 +9643,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920061</v>
+        <v>23330051920060</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -9666,16 +9666,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920061</v>
+        <v>23330051920060</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
@@ -9689,16 +9689,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920307</v>
+        <v>23330051920061</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
@@ -9712,16 +9712,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920307</v>
+        <v>23330051920061</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E21" t="s">
         <v>13</v>
@@ -9735,16 +9735,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920063</v>
+        <v>23330051920307</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -9758,16 +9758,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920063</v>
+        <v>23330051920307</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E23" t="s">
         <v>13</v>
@@ -9781,16 +9781,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920064</v>
+        <v>23330051920063</v>
       </c>
       <c r="B24" t="s">
         <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -9804,16 +9804,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920064</v>
+        <v>23330051920063</v>
       </c>
       <c r="B25" t="s">
         <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E25" t="s">
         <v>13</v>
@@ -9827,16 +9827,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920066</v>
+        <v>23330051920064</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
@@ -9850,16 +9850,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920066</v>
+        <v>23330051920064</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E27" t="s">
         <v>13</v>
@@ -9873,16 +9873,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920068</v>
+        <v>23330051920066</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
@@ -9896,16 +9896,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920068</v>
+        <v>23330051920066</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E29" t="s">
         <v>13</v>
@@ -9919,16 +9919,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920069</v>
+        <v>23330051920067</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
@@ -9942,16 +9942,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920069</v>
+        <v>23330051920067</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E31" t="s">
         <v>13</v>
@@ -9965,16 +9965,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920070</v>
+        <v>23330051920068</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
@@ -9988,16 +9988,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920070</v>
+        <v>23330051920068</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s">
         <v>13</v>
@@ -10011,16 +10011,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920272</v>
+        <v>23330051920069</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
@@ -10034,16 +10034,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920272</v>
+        <v>23330051920069</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E35" t="s">
         <v>13</v>
@@ -10057,16 +10057,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920074</v>
+        <v>23330051920070</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E36" t="s">
         <v>5</v>
@@ -10080,16 +10080,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920074</v>
+        <v>23330051920070</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E37" t="s">
         <v>13</v>
@@ -10103,16 +10103,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920075</v>
+        <v>23330051920272</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E38" t="s">
         <v>5</v>
@@ -10126,16 +10126,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920075</v>
+        <v>23330051920272</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C39" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E39" t="s">
         <v>13</v>
@@ -10144,6 +10144,98 @@
         <v>63</v>
       </c>
       <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>23330051920074</v>
+      </c>
+      <c r="B40" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" t="s">
+        <v>133</v>
+      </c>
+      <c r="D40" t="s">
+        <v>167</v>
+      </c>
+      <c r="E40" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" t="s">
+        <v>62</v>
+      </c>
+      <c r="G40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>23330051920074</v>
+      </c>
+      <c r="B41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" t="s">
+        <v>133</v>
+      </c>
+      <c r="D41" t="s">
+        <v>167</v>
+      </c>
+      <c r="E41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" t="s">
+        <v>63</v>
+      </c>
+      <c r="G41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>23330051920075</v>
+      </c>
+      <c r="B42" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" t="s">
+        <v>168</v>
+      </c>
+      <c r="E42" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>23330051920075</v>
+      </c>
+      <c r="B43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" t="s">
+        <v>168</v>
+      </c>
+      <c r="E43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" t="s">
+        <v>63</v>
+      </c>
+      <c r="G43">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHM - Estadisticos 20232.xlsx
+++ b/grupos/2ARHM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="139">
   <si>
     <t>Materia</t>
   </si>
@@ -206,30 +206,30 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Sanchez Morales Gilberto</t>
+  </si>
+  <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Loyo Sanchez Raul Manuel</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
@@ -245,24 +245,18 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>ANDRES</t>
   </si>
   <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
     <t>BACILIO</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
     <t>COLOHUA</t>
   </si>
   <si>
@@ -275,87 +269,57 @@
     <t>DIAZ</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
     <t>ESPIRITU</t>
   </si>
   <si>
+    <t>GUERRERO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>QUIROGA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SOSA</t>
+  </si>
+  <si>
+    <t>XALAMIHUA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GUERRERO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>QUIROGA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>CORDOVA</t>
   </si>
   <si>
-    <t>CALCANEO</t>
-  </si>
-  <si>
     <t>ATILANO</t>
   </si>
   <si>
-    <t>TECAMACHALTZI</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>TZANAHUA</t>
   </si>
   <si>
@@ -371,30 +335,18 @@
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>POOT</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>CANSECO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>AMADOR</t>
   </si>
   <si>
@@ -413,33 +365,21 @@
     <t>ARIAS</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>FIGUEROA</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
     <t>DAVID</t>
   </si>
   <si>
-    <t>YAELIS</t>
-  </si>
-  <si>
     <t>PAOLA</t>
   </si>
   <si>
-    <t>JEDIAEL</t>
-  </si>
-  <si>
-    <t>HUGO ISAI</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
     <t>ARIADNA</t>
   </si>
   <si>
@@ -455,27 +395,15 @@
     <t>CRIZULY AMITHAI</t>
   </si>
   <si>
-    <t>MARY CELESTE</t>
-  </si>
-  <si>
     <t>ADIEL ALONSO</t>
   </si>
   <si>
-    <t>LLUVIA ITZEL</t>
-  </si>
-  <si>
     <t>EUNICE</t>
   </si>
   <si>
     <t>REYNA IVETT</t>
   </si>
   <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MIGUEL ENRIQUE</t>
-  </si>
-  <si>
     <t>ANDREA</t>
   </si>
   <si>
@@ -485,15 +413,6 @@
     <t>KAROL BALAAM</t>
   </si>
   <si>
-    <t>MELANIE YARETZI</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
     <t>YASMIN</t>
   </si>
   <si>
@@ -510,15 +429,6 @@
   </si>
   <si>
     <t>SAMANTHA BETHANY</t>
-  </si>
-  <si>
-    <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>DIANA PAOLA</t>
   </si>
   <si>
     <t>MARIEL BIDEMI</t>
@@ -1062,7 +972,7 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1089,7 +999,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -1104,7 +1014,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -1143,7 +1053,7 @@
         <v>-1</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD4">
         <v>9</v>
@@ -1175,7 +1085,7 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1202,7 +1112,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -1217,7 +1127,7 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -1256,7 +1166,7 @@
         <v>-1</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD5">
         <v>5</v>
@@ -1271,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="AH5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI5">
         <v>8</v>
@@ -1288,7 +1198,7 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -1315,7 +1225,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -1330,7 +1240,7 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1369,7 +1279,7 @@
         <v>-1</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD6">
         <v>7</v>
@@ -1401,7 +1311,7 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1428,7 +1338,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1443,7 +1353,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -1482,7 +1392,7 @@
         <v>-1</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AD7">
         <v>5</v>
@@ -1514,7 +1424,7 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1541,7 +1451,7 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -1556,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -1595,7 +1505,7 @@
         <v>-1</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AD8">
         <v>5</v>
@@ -1610,7 +1520,7 @@
         <v>6</v>
       </c>
       <c r="AH8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI8">
         <v>5</v>
@@ -1627,7 +1537,7 @@
         <v>20</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1654,7 +1564,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>7</v>
@@ -1669,7 +1579,7 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>8</v>
@@ -1708,7 +1618,7 @@
         <v>-1</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD9">
         <v>6</v>
@@ -1723,7 +1633,7 @@
         <v>7</v>
       </c>
       <c r="AH9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI9">
         <v>7</v>
@@ -1740,7 +1650,7 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1767,7 +1677,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1782,7 +1692,7 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1821,7 +1731,7 @@
         <v>-1</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD10">
         <v>10</v>
@@ -1853,7 +1763,7 @@
         <v>22</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1880,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -1895,7 +1805,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1934,7 +1844,7 @@
         <v>-1</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD11">
         <v>7</v>
@@ -1966,7 +1876,7 @@
         <v>23</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1993,7 +1903,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>7</v>
@@ -2008,7 +1918,7 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -2047,7 +1957,7 @@
         <v>-1</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD12">
         <v>7</v>
@@ -2079,7 +1989,7 @@
         <v>24</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>6</v>
@@ -2106,7 +2016,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>8</v>
@@ -2121,7 +2031,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -2160,7 +2070,7 @@
         <v>-1</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD13">
         <v>7</v>
@@ -2192,7 +2102,7 @@
         <v>25</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -2219,7 +2129,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>8</v>
@@ -2234,7 +2144,7 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -2273,7 +2183,7 @@
         <v>-1</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD14">
         <v>7</v>
@@ -2288,7 +2198,7 @@
         <v>9</v>
       </c>
       <c r="AH14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI14">
         <v>10</v>
@@ -2305,7 +2215,7 @@
         <v>26</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -2332,7 +2242,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>8</v>
@@ -2347,7 +2257,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -2386,7 +2296,7 @@
         <v>-1</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD15">
         <v>8</v>
@@ -2418,7 +2328,7 @@
         <v>27</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -2445,7 +2355,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -2460,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>5</v>
@@ -2499,7 +2409,7 @@
         <v>-1</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD16">
         <v>5</v>
@@ -2531,7 +2441,7 @@
         <v>28</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -2558,7 +2468,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -2573,7 +2483,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>9</v>
@@ -2612,7 +2522,7 @@
         <v>-1</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD17">
         <v>5</v>
@@ -2627,7 +2537,7 @@
         <v>8</v>
       </c>
       <c r="AH17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI17">
         <v>7</v>
@@ -2644,7 +2554,7 @@
         <v>29</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -2671,7 +2581,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -2686,7 +2596,7 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2725,7 +2635,7 @@
         <v>-1</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD18">
         <v>8</v>
@@ -2757,7 +2667,7 @@
         <v>30</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -2784,7 +2694,7 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -2799,7 +2709,7 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -2838,7 +2748,7 @@
         <v>-1</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD19">
         <v>6</v>
@@ -2870,7 +2780,7 @@
         <v>31</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -2897,7 +2807,7 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>7</v>
@@ -2912,7 +2822,7 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2951,7 +2861,7 @@
         <v>-1</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD20">
         <v>6</v>
@@ -2983,7 +2893,7 @@
         <v>32</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -3010,7 +2920,7 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -3025,7 +2935,7 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>5</v>
@@ -3064,7 +2974,7 @@
         <v>-1</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD21">
         <v>5</v>
@@ -3096,7 +3006,7 @@
         <v>33</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -3123,7 +3033,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>7</v>
@@ -3138,7 +3048,7 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -3177,7 +3087,7 @@
         <v>-1</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD22">
         <v>7</v>
@@ -3209,7 +3119,7 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -3236,7 +3146,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>7</v>
@@ -3251,7 +3161,7 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -3290,7 +3200,7 @@
         <v>-1</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD23">
         <v>7</v>
@@ -3322,7 +3232,7 @@
         <v>35</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C24">
         <v>8</v>
@@ -3349,7 +3259,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -3364,7 +3274,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -3403,7 +3313,7 @@
         <v>-1</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD24">
         <v>9</v>
@@ -3418,7 +3328,7 @@
         <v>10</v>
       </c>
       <c r="AH24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI24">
         <v>10</v>
@@ -3435,7 +3345,7 @@
         <v>36</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -3462,7 +3372,7 @@
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -3477,7 +3387,7 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>8</v>
@@ -3516,7 +3426,7 @@
         <v>-1</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD25">
         <v>5</v>
@@ -3531,7 +3441,7 @@
         <v>8</v>
       </c>
       <c r="AH25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI25">
         <v>8</v>
@@ -3548,7 +3458,7 @@
         <v>37</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -3575,7 +3485,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>6</v>
@@ -3590,7 +3500,7 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>8</v>
@@ -3629,7 +3539,7 @@
         <v>-1</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD26">
         <v>6</v>
@@ -3644,7 +3554,7 @@
         <v>9</v>
       </c>
       <c r="AH26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI26">
         <v>9</v>
@@ -3661,7 +3571,7 @@
         <v>38</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>5</v>
@@ -3688,7 +3598,7 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -3703,7 +3613,7 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>8</v>
@@ -3742,7 +3652,7 @@
         <v>-1</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AD27">
         <v>5</v>
@@ -3774,7 +3684,7 @@
         <v>39</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -3801,7 +3711,7 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -3816,7 +3726,7 @@
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -3855,7 +3765,7 @@
         <v>-1</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD28">
         <v>6</v>
@@ -3887,7 +3797,7 @@
         <v>40</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -3914,7 +3824,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -3929,7 +3839,7 @@
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -3968,7 +3878,7 @@
         <v>-1</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD29">
         <v>6</v>
@@ -4000,7 +3910,7 @@
         <v>41</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -4027,7 +3937,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -4042,7 +3952,7 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -4081,7 +3991,7 @@
         <v>-1</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD30">
         <v>8</v>
@@ -4113,7 +4023,7 @@
         <v>42</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>8</v>
@@ -4140,7 +4050,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>8</v>
@@ -4155,7 +4065,7 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -4194,7 +4104,7 @@
         <v>-1</v>
       </c>
       <c r="AC31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD31">
         <v>8</v>
@@ -4226,7 +4136,7 @@
         <v>43</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -4253,7 +4163,7 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -4268,7 +4178,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -4307,7 +4217,7 @@
         <v>-1</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD32">
         <v>8</v>
@@ -4339,7 +4249,7 @@
         <v>44</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C33">
         <v>8</v>
@@ -4366,7 +4276,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -4381,7 +4291,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -4420,7 +4330,7 @@
         <v>-1</v>
       </c>
       <c r="AC33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD33">
         <v>9</v>
@@ -4452,7 +4362,7 @@
         <v>45</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C34">
         <v>5</v>
@@ -4479,7 +4389,7 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -4494,7 +4404,7 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -4533,7 +4443,7 @@
         <v>-1</v>
       </c>
       <c r="AC34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AD34">
         <v>5</v>
@@ -4565,7 +4475,7 @@
         <v>46</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C35">
         <v>5</v>
@@ -4592,7 +4502,7 @@
         <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -4607,7 +4517,7 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>7</v>
@@ -4646,7 +4556,7 @@
         <v>-1</v>
       </c>
       <c r="AC35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AD35">
         <v>5</v>
@@ -4661,7 +4571,7 @@
         <v>6</v>
       </c>
       <c r="AH35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI35">
         <v>6</v>
@@ -4678,7 +4588,7 @@
         <v>47</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>5</v>
@@ -4705,7 +4615,7 @@
         <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>5</v>
@@ -4720,7 +4630,7 @@
         <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>5</v>
@@ -4759,7 +4669,7 @@
         <v>-1</v>
       </c>
       <c r="AC36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD36">
         <v>5</v>
@@ -4774,7 +4684,7 @@
         <v>7</v>
       </c>
       <c r="AH36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI36">
         <v>5</v>
@@ -4791,7 +4701,7 @@
         <v>48</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C37">
         <v>7</v>
@@ -4818,7 +4728,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
         <v>9</v>
@@ -4833,7 +4743,7 @@
         <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
         <v>10</v>
@@ -4872,7 +4782,7 @@
         <v>-1</v>
       </c>
       <c r="AC37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD37">
         <v>8</v>
@@ -4904,7 +4814,7 @@
         <v>49</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -4931,7 +4841,7 @@
         <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>10</v>
@@ -4946,7 +4856,7 @@
         <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -4985,7 +4895,7 @@
         <v>-1</v>
       </c>
       <c r="AC38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AD38">
         <v>10</v>
@@ -5163,7 +5073,7 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -5190,7 +5100,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -5217,7 +5127,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -5249,7 +5159,7 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C5">
         <v>89.5</v>
@@ -5276,7 +5186,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L5">
         <v>90.7</v>
@@ -5303,7 +5213,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U5">
         <v>90.7</v>
@@ -5335,7 +5245,7 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C6">
         <v>94.7</v>
@@ -5362,7 +5272,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L6">
         <v>97.7</v>
@@ -5389,7 +5299,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U6">
         <v>97.7</v>
@@ -5421,7 +5331,7 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>84.2</v>
@@ -5448,7 +5358,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L7">
         <v>46.5</v>
@@ -5463,7 +5373,7 @@
         <v>85.7</v>
       </c>
       <c r="P7">
-        <v>73.3</v>
+        <v>40</v>
       </c>
       <c r="Q7">
         <v>40.6</v>
@@ -5475,7 +5385,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U7">
         <v>46.5</v>
@@ -5490,7 +5400,7 @@
         <v>85.7</v>
       </c>
       <c r="Y7">
-        <v>73.3</v>
+        <v>40</v>
       </c>
       <c r="Z7">
         <v>40.6</v>
@@ -5507,7 +5417,7 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C8">
         <v>84.2</v>
@@ -5534,7 +5444,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L8">
         <v>46.5</v>
@@ -5549,7 +5459,7 @@
         <v>85.7</v>
       </c>
       <c r="P8">
-        <v>86.7</v>
+        <v>46.7</v>
       </c>
       <c r="Q8">
         <v>43.8</v>
@@ -5561,7 +5471,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U8">
         <v>46.5</v>
@@ -5576,7 +5486,7 @@
         <v>85.7</v>
       </c>
       <c r="Y8">
-        <v>86.7</v>
+        <v>46.7</v>
       </c>
       <c r="Z8">
         <v>43.8</v>
@@ -5593,7 +5503,7 @@
         <v>20</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>89.5</v>
@@ -5620,7 +5530,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L9">
         <v>81.40000000000001</v>
@@ -5635,7 +5545,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>93.3</v>
+        <v>83.3</v>
       </c>
       <c r="Q9">
         <v>87.5</v>
@@ -5647,7 +5557,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U9">
         <v>81.40000000000001</v>
@@ -5662,7 +5572,7 @@
         <v>100</v>
       </c>
       <c r="Y9">
-        <v>93.3</v>
+        <v>83.3</v>
       </c>
       <c r="Z9">
         <v>87.5</v>
@@ -5679,7 +5589,7 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -5706,7 +5616,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -5733,7 +5643,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -5765,7 +5675,7 @@
         <v>22</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -5792,7 +5702,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -5819,7 +5729,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -5851,7 +5761,7 @@
         <v>23</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -5878,7 +5788,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -5905,7 +5815,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -5937,7 +5847,7 @@
         <v>24</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -5964,7 +5874,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -5991,7 +5901,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -6023,7 +5933,7 @@
         <v>25</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -6050,7 +5960,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -6065,7 +5975,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="Q14">
         <v>90.59999999999999</v>
@@ -6077,7 +5987,7 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -6092,7 +6002,7 @@
         <v>100</v>
       </c>
       <c r="Y14">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="Z14">
         <v>90.59999999999999</v>
@@ -6109,7 +6019,7 @@
         <v>26</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -6136,7 +6046,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -6163,7 +6073,7 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -6195,7 +6105,7 @@
         <v>27</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C16">
         <v>89.5</v>
@@ -6222,7 +6132,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L16">
         <v>62.8</v>
@@ -6237,7 +6147,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="P16">
-        <v>86.7</v>
+        <v>70</v>
       </c>
       <c r="Q16">
         <v>81.3</v>
@@ -6249,7 +6159,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U16">
         <v>62.8</v>
@@ -6264,7 +6174,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="Y16">
-        <v>86.7</v>
+        <v>70</v>
       </c>
       <c r="Z16">
         <v>81.3</v>
@@ -6281,7 +6191,7 @@
         <v>28</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C17">
         <v>89.5</v>
@@ -6308,7 +6218,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L17">
         <v>81.40000000000001</v>
@@ -6335,7 +6245,7 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U17">
         <v>81.40000000000001</v>
@@ -6367,7 +6277,7 @@
         <v>29</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -6394,7 +6304,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -6421,7 +6331,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -6453,7 +6363,7 @@
         <v>30</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -6480,7 +6390,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -6507,7 +6417,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -6539,7 +6449,7 @@
         <v>31</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C20">
         <v>84.2</v>
@@ -6566,7 +6476,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L20">
         <v>93</v>
@@ -6593,7 +6503,7 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U20">
         <v>93</v>
@@ -6625,7 +6535,7 @@
         <v>32</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C21">
         <v>84.2</v>
@@ -6652,7 +6562,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L21">
         <v>60.5</v>
@@ -6679,7 +6589,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U21">
         <v>60.5</v>
@@ -6711,7 +6621,7 @@
         <v>33</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -6738,7 +6648,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -6753,7 +6663,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Q22">
         <v>96.90000000000001</v>
@@ -6765,7 +6675,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -6780,7 +6690,7 @@
         <v>100</v>
       </c>
       <c r="Y22">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Z22">
         <v>96.90000000000001</v>
@@ -6797,7 +6707,7 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -6824,7 +6734,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -6839,7 +6749,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -6851,7 +6761,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -6866,7 +6776,7 @@
         <v>100</v>
       </c>
       <c r="Y23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Z23">
         <v>100</v>
@@ -6883,7 +6793,7 @@
         <v>35</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -6910,7 +6820,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -6937,7 +6847,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -6969,7 +6879,7 @@
         <v>36</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -6996,7 +6906,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -7023,7 +6933,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -7055,7 +6965,7 @@
         <v>37</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -7082,7 +6992,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -7109,7 +7019,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -7141,7 +7051,7 @@
         <v>38</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C27">
         <v>94.7</v>
@@ -7168,7 +7078,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L27">
         <v>97.7</v>
@@ -7195,7 +7105,7 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U27">
         <v>97.7</v>
@@ -7227,7 +7137,7 @@
         <v>39</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -7254,7 +7164,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -7281,7 +7191,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -7313,7 +7223,7 @@
         <v>40</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -7340,7 +7250,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -7367,7 +7277,7 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -7399,7 +7309,7 @@
         <v>41</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -7426,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -7453,7 +7363,7 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -7485,7 +7395,7 @@
         <v>42</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -7512,7 +7422,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -7539,7 +7449,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -7571,7 +7481,7 @@
         <v>43</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -7598,7 +7508,7 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -7625,7 +7535,7 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -7657,7 +7567,7 @@
         <v>44</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -7684,7 +7594,7 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -7711,7 +7621,7 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U33">
         <v>100</v>
@@ -7743,7 +7653,7 @@
         <v>45</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C34">
         <v>84.2</v>
@@ -7770,7 +7680,7 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L34">
         <v>93</v>
@@ -7785,7 +7695,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -7797,7 +7707,7 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U34">
         <v>93</v>
@@ -7812,7 +7722,7 @@
         <v>100</v>
       </c>
       <c r="Y34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Z34">
         <v>100</v>
@@ -7829,7 +7739,7 @@
         <v>46</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C35">
         <v>63.2</v>
@@ -7856,7 +7766,7 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L35">
         <v>60.5</v>
@@ -7871,7 +7781,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="Q35">
         <v>87.5</v>
@@ -7883,7 +7793,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="U35">
         <v>60.5</v>
@@ -7898,7 +7808,7 @@
         <v>100</v>
       </c>
       <c r="Y35">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="Z35">
         <v>87.5</v>
@@ -7915,7 +7825,7 @@
         <v>47</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C36">
         <v>63.2</v>
@@ -7942,7 +7852,7 @@
         <v>100</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L36">
         <v>51.2</v>
@@ -7957,7 +7867,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="Q36">
         <v>87.5</v>
@@ -7969,7 +7879,7 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U36">
         <v>51.2</v>
@@ -7984,7 +7894,7 @@
         <v>100</v>
       </c>
       <c r="Y36">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="Z36">
         <v>87.5</v>
@@ -8001,7 +7911,7 @@
         <v>48</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -8028,7 +7938,7 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -8043,7 +7953,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -8055,7 +7965,7 @@
         <v>100</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U37">
         <v>100</v>
@@ -8070,7 +7980,7 @@
         <v>100</v>
       </c>
       <c r="Y37">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Z37">
         <v>100</v>
@@ -8087,7 +7997,7 @@
         <v>49</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -8114,7 +8024,7 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L38">
         <v>100</v>
@@ -8141,7 +8051,7 @@
         <v>100</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -8222,7 +8132,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -8251,7 +8161,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -8260,27 +8170,30 @@
         <v>35</v>
       </c>
       <c r="D3">
+        <v>24</v>
+      </c>
+      <c r="E3">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="G3" s="2">
+        <v>31.4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3" s="2">
         <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>35</v>
-      </c>
-      <c r="J3" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -8301,7 +8214,7 @@
         <v>31.4</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8312,7 +8225,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -8333,7 +8246,7 @@
         <v>31.4</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8344,7 +8257,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -8353,19 +8266,19 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>68.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="G6" s="2">
-        <v>31.4</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8376,7 +8289,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -8385,19 +8298,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="G7" s="2">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8408,7 +8321,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
@@ -8417,19 +8330,19 @@
         <v>35</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2">
-        <v>85.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>14.3</v>
+        <v>11.4</v>
       </c>
       <c r="H8">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8440,7 +8353,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
@@ -8449,16 +8362,16 @@
         <v>35</v>
       </c>
       <c r="D9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="G9" s="2">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="H9">
         <v>8</v>
@@ -8509,7 +8422,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8536,706 +8449,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920048</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>23330051920049</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>23330051920050</v>
-      </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>23330051920051</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>23330051920052</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>23330051920083</v>
-      </c>
-      <c r="B7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920053</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>23330051920054</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>23330051920055</v>
-      </c>
-      <c r="B10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>23330051920056</v>
-      </c>
-      <c r="B11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>23330051920057</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>23330051920351</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>23330051920058</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>23330051920246</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920060</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" t="s">
-        <v>148</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920061</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920062</v>
-      </c>
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>23330051920254</v>
-      </c>
-      <c r="B19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920307</v>
-      </c>
-      <c r="B20" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" t="s">
-        <v>121</v>
-      </c>
-      <c r="D20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>23330051920063</v>
-      </c>
-      <c r="B21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>23330051920064</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>23330051920259</v>
-      </c>
-      <c r="B23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" t="s">
-        <v>155</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23330051920065</v>
-      </c>
-      <c r="B24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23330051920263</v>
-      </c>
-      <c r="B25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" t="s">
-        <v>157</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>23330051920066</v>
-      </c>
-      <c r="B26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" t="s">
-        <v>158</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920067</v>
-      </c>
-      <c r="B27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" t="s">
-        <v>159</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920068</v>
-      </c>
-      <c r="B28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C28" t="s">
-        <v>127</v>
-      </c>
-      <c r="D28" t="s">
-        <v>160</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>23330051920069</v>
-      </c>
-      <c r="B29" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" t="s">
-        <v>161</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>23330051920070</v>
-      </c>
-      <c r="B30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" t="s">
-        <v>129</v>
-      </c>
-      <c r="D30" t="s">
-        <v>162</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>23330051920272</v>
-      </c>
-      <c r="B31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" t="s">
-        <v>163</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>23330051920071</v>
-      </c>
-      <c r="B32" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" t="s">
-        <v>164</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>23330051920072</v>
-      </c>
-      <c r="B33" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" t="s">
-        <v>165</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>23330051920073</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" t="s">
-        <v>166</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>23330051920074</v>
-      </c>
-      <c r="B35" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" t="s">
-        <v>133</v>
-      </c>
-      <c r="D35" t="s">
-        <v>167</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>23330051920075</v>
-      </c>
-      <c r="B36" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" t="s">
-        <v>113</v>
-      </c>
-      <c r="D36" t="s">
-        <v>168</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9243,7 +8456,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9275,45 +8488,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920048</v>
+        <v>23330051920062</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920048</v>
+        <v>23330051920062</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -9321,45 +8534,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920050</v>
+        <v>23330051920065</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920050</v>
+        <v>23330051920065</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -9367,19 +8580,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920053</v>
+        <v>23330051920048</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
         <v>62</v>
@@ -9390,22 +8603,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920053</v>
+        <v>23330051920050</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -9413,19 +8626,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920054</v>
+        <v>23330051920053</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
         <v>62</v>
@@ -9439,19 +8652,19 @@
         <v>23330051920054</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -9462,16 +8675,16 @@
         <v>23330051920055</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
         <v>62</v>
@@ -9482,22 +8695,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920055</v>
+        <v>23330051920056</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -9505,19 +8718,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920056</v>
+        <v>23330051920057</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
         <v>62</v>
@@ -9528,22 +8741,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920056</v>
+        <v>23330051920058</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -9551,19 +8764,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920057</v>
+        <v>23330051920060</v>
       </c>
       <c r="B14" t="s">
         <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
         <v>62</v>
@@ -9574,22 +8787,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920057</v>
+        <v>23330051920061</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -9597,19 +8810,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920058</v>
+        <v>23330051920307</v>
       </c>
       <c r="B16" t="s">
         <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
@@ -9620,22 +8833,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920058</v>
+        <v>23330051920063</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -9643,19 +8856,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920060</v>
+        <v>23330051920064</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s">
         <v>62</v>
@@ -9666,22 +8879,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920060</v>
+        <v>23330051920066</v>
       </c>
       <c r="B19" t="s">
         <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -9689,19 +8902,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920061</v>
+        <v>23330051920067</v>
       </c>
       <c r="B20" t="s">
         <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
         <v>62</v>
@@ -9712,22 +8925,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920061</v>
+        <v>23330051920068</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
         <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -9735,19 +8948,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920307</v>
+        <v>23330051920069</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
         <v>62</v>
@@ -9758,22 +8971,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920307</v>
+        <v>23330051920070</v>
       </c>
       <c r="B23" t="s">
         <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s">
         <v>13</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -9781,19 +8994,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920063</v>
+        <v>23330051920272</v>
       </c>
       <c r="B24" t="s">
         <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F24" t="s">
         <v>62</v>
@@ -9804,22 +9017,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920063</v>
+        <v>23330051920074</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="E25" t="s">
         <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G25">
         <v>-1</v>
@@ -9827,415 +9040,24 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920064</v>
+        <v>23330051920075</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F26" t="s">
         <v>62</v>
       </c>
       <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920064</v>
-      </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" t="s">
-        <v>63</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920066</v>
-      </c>
-      <c r="B28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" t="s">
-        <v>158</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920066</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" t="s">
-        <v>158</v>
-      </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" t="s">
-        <v>63</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>23330051920067</v>
-      </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" t="s">
-        <v>159</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>23330051920067</v>
-      </c>
-      <c r="B31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" t="s">
-        <v>159</v>
-      </c>
-      <c r="E31" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" t="s">
-        <v>63</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>23330051920068</v>
-      </c>
-      <c r="B32" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>23330051920068</v>
-      </c>
-      <c r="B33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" t="s">
-        <v>63</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>23330051920069</v>
-      </c>
-      <c r="B34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>23330051920069</v>
-      </c>
-      <c r="B35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D35" t="s">
-        <v>161</v>
-      </c>
-      <c r="E35" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" t="s">
-        <v>63</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>23330051920070</v>
-      </c>
-      <c r="B36" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" t="s">
-        <v>129</v>
-      </c>
-      <c r="D36" t="s">
-        <v>162</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>23330051920070</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" t="s">
-        <v>162</v>
-      </c>
-      <c r="E37" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" t="s">
-        <v>63</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>23330051920272</v>
-      </c>
-      <c r="B38" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" t="s">
-        <v>130</v>
-      </c>
-      <c r="D38" t="s">
-        <v>163</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>23330051920272</v>
-      </c>
-      <c r="B39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" t="s">
-        <v>130</v>
-      </c>
-      <c r="D39" t="s">
-        <v>163</v>
-      </c>
-      <c r="E39" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" t="s">
-        <v>63</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>23330051920074</v>
-      </c>
-      <c r="B40" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" t="s">
-        <v>167</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>23330051920074</v>
-      </c>
-      <c r="B41" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" t="s">
-        <v>133</v>
-      </c>
-      <c r="D41" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" t="s">
-        <v>63</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>23330051920075</v>
-      </c>
-      <c r="B42" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" t="s">
-        <v>113</v>
-      </c>
-      <c r="D42" t="s">
-        <v>168</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>62</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>23330051920075</v>
-      </c>
-      <c r="B43" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" t="s">
-        <v>113</v>
-      </c>
-      <c r="D43" t="s">
-        <v>168</v>
-      </c>
-      <c r="E43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" t="s">
-        <v>63</v>
-      </c>
-      <c r="G43">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHM - Estadisticos 20232.xlsx
+++ b/grupos/2ARHM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="153">
   <si>
     <t>Materia</t>
   </si>
@@ -209,30 +209,30 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Sanchez Morales Gilberto</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
+    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>Loyo Sanchez Raul Manuel</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -245,43 +245,58 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUERRERO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>GUERRERO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>OLMOS</t>
   </si>
   <si>
     <t>PALOMARES</t>
@@ -308,43 +323,52 @@
     <t>XALAMIHUA</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>CALCANEO</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>POOT</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>POOT</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>AMADOR</t>
@@ -368,49 +392,64 @@
     <t>FIGUEROA</t>
   </si>
   <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAELIS</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>MAR EDITH</t>
+  </si>
+  <si>
+    <t>MELISA</t>
+  </si>
+  <si>
+    <t>JUAN ALONSO</t>
+  </si>
+  <si>
+    <t>CRIZULY AMITHAI</t>
+  </si>
+  <si>
+    <t>ADIEL ALONSO</t>
+  </si>
+  <si>
+    <t>LLUVIA ITZEL</t>
+  </si>
+  <si>
+    <t>EUNICE</t>
+  </si>
+  <si>
+    <t>REYNA IVETT</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>HANNA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>KAROL BALAAM</t>
+  </si>
+  <si>
+    <t>MELANIE YARETZI</t>
+  </si>
+  <si>
     <t>DENISSE</t>
   </si>
   <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>MAR EDITH</t>
-  </si>
-  <si>
-    <t>MELISA</t>
-  </si>
-  <si>
-    <t>JUAN ALONSO</t>
-  </si>
-  <si>
-    <t>CRIZULY AMITHAI</t>
-  </si>
-  <si>
-    <t>ADIEL ALONSO</t>
-  </si>
-  <si>
-    <t>EUNICE</t>
-  </si>
-  <si>
-    <t>REYNA IVETT</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>HANNA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>KAROL BALAAM</t>
+    <t>ANGEL GABRIEL</t>
   </si>
   <si>
     <t>YASMIN</t>
@@ -429,6 +468,9 @@
   </si>
   <si>
     <t>SAMANTHA BETHANY</t>
+  </si>
+  <si>
+    <t>IVONNE ERIMAR</t>
   </si>
   <si>
     <t>MARIEL BIDEMI</t>
@@ -1029,28 +1071,28 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>10</v>
@@ -1142,52 +1184,52 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC5">
         <v>7</v>
       </c>
       <c r="AD5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5">
         <v>6</v>
       </c>
       <c r="AF5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI5">
         <v>8</v>
       </c>
       <c r="AJ5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK5">
         <v>-1</v>
@@ -1255,28 +1297,28 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1294,7 +1336,7 @@
         <v>9</v>
       </c>
       <c r="AH6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI6">
         <v>10</v>
@@ -1368,28 +1410,28 @@
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC7">
         <v>5</v>
@@ -1404,7 +1446,7 @@
         <v>5</v>
       </c>
       <c r="AG7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH7">
         <v>5</v>
@@ -1481,28 +1523,28 @@
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1517,7 +1559,7 @@
         <v>5</v>
       </c>
       <c r="AG8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH8">
         <v>5</v>
@@ -1594,28 +1636,28 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -1624,13 +1666,13 @@
         <v>6</v>
       </c>
       <c r="AE9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH9">
         <v>7</v>
@@ -1639,7 +1681,7 @@
         <v>7</v>
       </c>
       <c r="AJ9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK9">
         <v>-1</v>
@@ -1707,28 +1749,28 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>9</v>
@@ -1820,28 +1862,28 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -1933,28 +1975,28 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>9</v>
@@ -1963,7 +2005,7 @@
         <v>7</v>
       </c>
       <c r="AE12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF12">
         <v>10</v>
@@ -1972,7 +2014,7 @@
         <v>10</v>
       </c>
       <c r="AH12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI12">
         <v>10</v>
@@ -2046,34 +2088,34 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>8</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE13">
         <v>8</v>
@@ -2091,7 +2133,7 @@
         <v>10</v>
       </c>
       <c r="AJ13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK13">
         <v>-1</v>
@@ -2159,46 +2201,46 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>8</v>
       </c>
       <c r="AD14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE14">
         <v>6</v>
       </c>
       <c r="AF14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI14">
         <v>10</v>
@@ -2272,28 +2314,28 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC15">
         <v>9</v>
@@ -2302,7 +2344,7 @@
         <v>8</v>
       </c>
       <c r="AE15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF15">
         <v>10</v>
@@ -2385,28 +2427,28 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC16">
         <v>7</v>
@@ -2498,34 +2540,34 @@
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>7</v>
       </c>
       <c r="AD17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE17">
         <v>6</v>
@@ -2540,10 +2582,10 @@
         <v>7</v>
       </c>
       <c r="AI17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK17">
         <v>-1</v>
@@ -2611,28 +2653,28 @@
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -2724,34 +2766,34 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>8</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE19">
         <v>8</v>
@@ -2763,7 +2805,7 @@
         <v>9</v>
       </c>
       <c r="AH19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI19">
         <v>10</v>
@@ -2837,28 +2879,28 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC20">
         <v>8</v>
@@ -2867,7 +2909,7 @@
         <v>6</v>
       </c>
       <c r="AE20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF20">
         <v>7</v>
@@ -2879,7 +2921,7 @@
         <v>8</v>
       </c>
       <c r="AI20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ20">
         <v>7</v>
@@ -2950,28 +2992,28 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -2986,7 +3028,7 @@
         <v>5</v>
       </c>
       <c r="AG21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH21">
         <v>5</v>
@@ -2995,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="AJ21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK21">
         <v>-1</v>
@@ -3063,37 +3105,37 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>8</v>
       </c>
       <c r="AD22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF22">
         <v>8</v>
@@ -3102,13 +3144,13 @@
         <v>9</v>
       </c>
       <c r="AH22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI22">
         <v>10</v>
       </c>
       <c r="AJ22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK22">
         <v>-1</v>
@@ -3176,40 +3218,40 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>9</v>
       </c>
       <c r="AD23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG23">
         <v>9</v>
@@ -3221,7 +3263,7 @@
         <v>9</v>
       </c>
       <c r="AJ23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK23">
         <v>-1</v>
@@ -3289,28 +3331,28 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC24">
         <v>10</v>
@@ -3402,37 +3444,37 @@
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>8</v>
       </c>
       <c r="AD25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF25">
         <v>6</v>
@@ -3441,7 +3483,7 @@
         <v>8</v>
       </c>
       <c r="AH25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI25">
         <v>8</v>
@@ -3515,28 +3557,28 @@
         <v>-1</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC26">
         <v>7</v>
@@ -3548,19 +3590,19 @@
         <v>6</v>
       </c>
       <c r="AF26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI26">
         <v>9</v>
       </c>
       <c r="AJ26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK26">
         <v>-1</v>
@@ -3628,40 +3670,40 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>6</v>
       </c>
       <c r="AD27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG27">
         <v>6</v>
@@ -3673,7 +3715,7 @@
         <v>7</v>
       </c>
       <c r="AJ27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK27">
         <v>-1</v>
@@ -3741,37 +3783,37 @@
         <v>-1</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC28">
         <v>7</v>
       </c>
       <c r="AD28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF28">
         <v>10</v>
@@ -3854,37 +3896,37 @@
         <v>-1</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>9</v>
       </c>
       <c r="AD29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF29">
         <v>10</v>
@@ -3899,7 +3941,7 @@
         <v>10</v>
       </c>
       <c r="AJ29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK29">
         <v>-1</v>
@@ -3967,34 +4009,34 @@
         <v>-1</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC30">
         <v>10</v>
       </c>
       <c r="AD30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE30">
         <v>8</v>
@@ -4006,13 +4048,13 @@
         <v>9</v>
       </c>
       <c r="AH30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI30">
         <v>10</v>
       </c>
       <c r="AJ30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK30">
         <v>-1</v>
@@ -4080,34 +4122,34 @@
         <v>-1</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>8</v>
       </c>
       <c r="AD31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE31">
         <v>8</v>
@@ -4125,7 +4167,7 @@
         <v>10</v>
       </c>
       <c r="AJ31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK31">
         <v>-1</v>
@@ -4193,34 +4235,34 @@
         <v>-1</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC32">
         <v>9</v>
       </c>
       <c r="AD32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE32">
         <v>9</v>
@@ -4306,28 +4348,28 @@
         <v>-1</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC33">
         <v>8</v>
@@ -4419,52 +4461,52 @@
         <v>-1</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC34">
         <v>6</v>
       </c>
       <c r="AD34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF34">
         <v>7</v>
       </c>
       <c r="AG34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI34">
         <v>9</v>
       </c>
       <c r="AJ34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK34">
         <v>-1</v>
@@ -4532,28 +4574,28 @@
         <v>-1</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC35">
         <v>7</v>
@@ -4562,7 +4604,7 @@
         <v>5</v>
       </c>
       <c r="AE35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF35">
         <v>7</v>
@@ -4571,10 +4613,10 @@
         <v>6</v>
       </c>
       <c r="AH35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ35">
         <v>5</v>
@@ -4645,28 +4687,28 @@
         <v>-1</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC36">
         <v>8</v>
@@ -4675,19 +4717,19 @@
         <v>5</v>
       </c>
       <c r="AE36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG36">
         <v>7</v>
       </c>
       <c r="AH36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ36">
         <v>5</v>
@@ -4758,34 +4800,34 @@
         <v>-1</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC37">
         <v>10</v>
       </c>
       <c r="AD37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE37">
         <v>9</v>
@@ -4871,28 +4913,28 @@
         <v>-1</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC38">
         <v>8</v>
@@ -5216,10 +5258,10 @@
         <v>85</v>
       </c>
       <c r="U5">
-        <v>90.7</v>
+        <v>93.7</v>
       </c>
       <c r="V5">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="W5">
         <v>100</v>
@@ -5228,13 +5270,13 @@
         <v>100</v>
       </c>
       <c r="Y5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Z5">
         <v>93.8</v>
       </c>
       <c r="AA5">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="AB5">
         <v>100</v>
@@ -5302,7 +5344,7 @@
         <v>90</v>
       </c>
       <c r="U6">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -5317,7 +5359,7 @@
         <v>100</v>
       </c>
       <c r="Z6">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AA6">
         <v>100</v>
@@ -5388,28 +5430,28 @@
         <v>80</v>
       </c>
       <c r="U7">
-        <v>46.5</v>
+        <v>31.7</v>
       </c>
       <c r="V7">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="W7">
-        <v>90</v>
+        <v>62.5</v>
       </c>
       <c r="X7">
-        <v>85.7</v>
+        <v>53.6</v>
       </c>
       <c r="Y7">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Z7">
-        <v>40.6</v>
+        <v>27.1</v>
       </c>
       <c r="AA7">
-        <v>55</v>
+        <v>34.4</v>
       </c>
       <c r="AB7">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -5474,28 +5516,28 @@
         <v>80</v>
       </c>
       <c r="U8">
-        <v>46.5</v>
+        <v>31.7</v>
       </c>
       <c r="V8">
-        <v>65</v>
+        <v>40.6</v>
       </c>
       <c r="W8">
-        <v>90</v>
+        <v>62.5</v>
       </c>
       <c r="X8">
-        <v>85.7</v>
+        <v>53.6</v>
       </c>
       <c r="Y8">
-        <v>46.7</v>
+        <v>29.2</v>
       </c>
       <c r="Z8">
-        <v>43.8</v>
+        <v>29.2</v>
       </c>
       <c r="AA8">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="AB8">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -5560,25 +5602,25 @@
         <v>90</v>
       </c>
       <c r="U9">
-        <v>81.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="V9">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="W9">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="X9">
         <v>100</v>
       </c>
       <c r="Y9">
-        <v>83.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Z9">
         <v>87.5</v>
       </c>
       <c r="AA9">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AB9">
         <v>100</v>
@@ -5744,7 +5786,7 @@
         <v>100</v>
       </c>
       <c r="Y11">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z11">
         <v>100</v>
@@ -5833,10 +5875,10 @@
         <v>100</v>
       </c>
       <c r="Z12">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AA12">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AB12">
         <v>100</v>
@@ -5922,7 +5964,7 @@
         <v>100</v>
       </c>
       <c r="AA13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AB13">
         <v>100</v>
@@ -5996,19 +6038,19 @@
         <v>100</v>
       </c>
       <c r="W14">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="X14">
         <v>100</v>
       </c>
       <c r="Y14">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="Z14">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="AA14">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AB14">
         <v>100</v>
@@ -6162,28 +6204,28 @@
         <v>85</v>
       </c>
       <c r="U16">
-        <v>62.8</v>
+        <v>42.9</v>
       </c>
       <c r="V16">
-        <v>70</v>
+        <v>43.8</v>
       </c>
       <c r="W16">
-        <v>92</v>
+        <v>57.5</v>
       </c>
       <c r="X16">
-        <v>92.90000000000001</v>
+        <v>58</v>
       </c>
       <c r="Y16">
-        <v>70</v>
+        <v>43.8</v>
       </c>
       <c r="Z16">
-        <v>81.3</v>
+        <v>54.2</v>
       </c>
       <c r="AA16">
-        <v>95</v>
+        <v>59.4</v>
       </c>
       <c r="AB16">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="17" spans="1:28">
@@ -6248,10 +6290,10 @@
         <v>85</v>
       </c>
       <c r="U17">
-        <v>81.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="V17">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="W17">
         <v>100</v>
@@ -6260,13 +6302,13 @@
         <v>100</v>
       </c>
       <c r="Y17">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="Z17">
         <v>100</v>
       </c>
       <c r="AA17">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AB17">
         <v>100</v>
@@ -6349,10 +6391,10 @@
         <v>100</v>
       </c>
       <c r="Z18">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AA18">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AB18">
         <v>100</v>
@@ -6435,7 +6477,7 @@
         <v>100</v>
       </c>
       <c r="Z19">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AA19">
         <v>100</v>
@@ -6506,7 +6548,7 @@
         <v>85</v>
       </c>
       <c r="U20">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -6521,7 +6563,7 @@
         <v>100</v>
       </c>
       <c r="Z20">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AA20">
         <v>100</v>
@@ -6592,25 +6634,25 @@
         <v>85</v>
       </c>
       <c r="U21">
-        <v>60.5</v>
+        <v>73</v>
       </c>
       <c r="V21">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="W21">
-        <v>85</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="X21">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="Y21">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="Z21">
-        <v>43.8</v>
+        <v>62.5</v>
       </c>
       <c r="AA21">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AB21">
         <v>100</v>
@@ -6684,19 +6726,19 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X22">
         <v>100</v>
       </c>
       <c r="Y22">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="Z22">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AA22">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="AB22">
         <v>100</v>
@@ -6770,13 +6812,13 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="X23">
         <v>100</v>
       </c>
       <c r="Y23">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="Z23">
         <v>100</v>
@@ -6939,10 +6981,10 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="W25">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X25">
         <v>100</v>
@@ -6951,7 +6993,7 @@
         <v>100</v>
       </c>
       <c r="Z25">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AA25">
         <v>100</v>
@@ -7025,10 +7067,10 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="W26">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="X26">
         <v>100</v>
@@ -7040,7 +7082,7 @@
         <v>93.8</v>
       </c>
       <c r="AA26">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AB26">
         <v>100</v>
@@ -7108,13 +7150,13 @@
         <v>80</v>
       </c>
       <c r="U27">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V27">
         <v>100</v>
       </c>
       <c r="W27">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X27">
         <v>100</v>
@@ -7123,10 +7165,10 @@
         <v>100</v>
       </c>
       <c r="Z27">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="AA27">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="AB27">
         <v>100</v>
@@ -7292,13 +7334,13 @@
         <v>100</v>
       </c>
       <c r="Y29">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z29">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AA29">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AB29">
         <v>100</v>
@@ -7470,7 +7512,7 @@
         <v>100</v>
       </c>
       <c r="AA31">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AB31">
         <v>100</v>
@@ -7710,25 +7752,25 @@
         <v>85</v>
       </c>
       <c r="U34">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="V34">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="W34">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="X34">
         <v>100</v>
       </c>
       <c r="Y34">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Z34">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="AA34">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="AB34">
         <v>100</v>
@@ -7796,10 +7838,10 @@
         <v>85</v>
       </c>
       <c r="U35">
-        <v>60.5</v>
+        <v>54</v>
       </c>
       <c r="V35">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="W35">
         <v>100</v>
@@ -7808,13 +7850,13 @@
         <v>100</v>
       </c>
       <c r="Y35">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="Z35">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="AA35">
-        <v>90</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AB35">
         <v>100</v>
@@ -7882,25 +7924,25 @@
         <v>90</v>
       </c>
       <c r="U36">
-        <v>51.2</v>
+        <v>47.6</v>
       </c>
       <c r="V36">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="W36">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="X36">
         <v>100</v>
       </c>
       <c r="Y36">
-        <v>96.7</v>
+        <v>93.8</v>
       </c>
       <c r="Z36">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AA36">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="AB36">
         <v>100</v>
@@ -7980,7 +8022,7 @@
         <v>100</v>
       </c>
       <c r="Y37">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="Z37">
         <v>100</v>
@@ -8161,7 +8203,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -8170,16 +8212,16 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>68.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>31.4</v>
+        <v>17.1</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -8193,7 +8235,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -8202,19 +8244,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>68.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="G4" s="2">
-        <v>31.4</v>
+        <v>14.3</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8225,7 +8267,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -8234,19 +8276,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>68.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>31.4</v>
+        <v>11.4</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8266,19 +8308,19 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>20</v>
+        <v>11.4</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8289,7 +8331,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -8298,19 +8340,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>85.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>14.3</v>
+        <v>11.4</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8321,7 +8363,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
@@ -8342,7 +8384,7 @@
         <v>11.4</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8353,7 +8395,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
@@ -8362,19 +8404,19 @@
         <v>35</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>94.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -8385,7 +8427,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
@@ -8394,19 +8436,19 @@
         <v>35</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2">
-        <v>97.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="G10" s="2">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="H10">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -8456,7 +8498,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8488,39 +8530,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920062</v>
+        <v>23330051920048</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920062</v>
+        <v>23330051920049</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -8534,39 +8576,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920065</v>
+        <v>23330051920050</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920065</v>
+        <v>23330051920083</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -8580,16 +8622,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920048</v>
+        <v>23330051920053</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -8603,16 +8645,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920050</v>
+        <v>23330051920054</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -8626,16 +8668,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920053</v>
+        <v>23330051920055</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -8649,16 +8691,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920054</v>
+        <v>23330051920056</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -8672,16 +8714,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920055</v>
+        <v>23330051920057</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -8695,16 +8737,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920056</v>
+        <v>23330051920058</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -8718,16 +8760,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920057</v>
+        <v>23330051920246</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
@@ -8741,16 +8783,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920058</v>
+        <v>23330051920060</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -8764,16 +8806,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920060</v>
+        <v>23330051920061</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
@@ -8787,16 +8829,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920061</v>
+        <v>23330051920062</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
@@ -8813,13 +8855,13 @@
         <v>23330051920307</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
@@ -8836,13 +8878,13 @@
         <v>23330051920063</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
         <v>13</v>
@@ -8859,13 +8901,13 @@
         <v>23330051920064</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
@@ -8879,16 +8921,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920066</v>
+        <v>23330051920259</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E19" t="s">
         <v>13</v>
@@ -8902,16 +8944,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920067</v>
+        <v>23330051920065</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E20" t="s">
         <v>13</v>
@@ -8925,16 +8967,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920068</v>
+        <v>23330051920263</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E21" t="s">
         <v>13</v>
@@ -8948,16 +8990,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920069</v>
+        <v>23330051920066</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
         <v>13</v>
@@ -8971,16 +9013,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920070</v>
+        <v>23330051920067</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
         <v>13</v>
@@ -8994,16 +9036,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920272</v>
+        <v>23330051920068</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
         <v>13</v>
@@ -9017,16 +9059,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920074</v>
+        <v>23330051920069</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E25" t="s">
         <v>13</v>
@@ -9040,16 +9082,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920075</v>
+        <v>23330051920070</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E26" t="s">
         <v>13</v>
@@ -9058,6 +9100,98 @@
         <v>62</v>
       </c>
       <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920272</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920071</v>
+      </c>
+      <c r="B28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>23330051920074</v>
+      </c>
+      <c r="B29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>23330051920075</v>
+      </c>
+      <c r="B30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHM - Estadisticos 20232.xlsx
+++ b/grupos/2ARHM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -206,9 +206,6 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
@@ -230,6 +227,9 @@
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Loyo Sanchez Raul Manuel</t>
   </si>
   <si>
@@ -245,238 +245,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ANDRES</t>
+    <t>ROJAS</t>
   </si>
   <si>
-    <t>ARENAS</t>
+    <t>SANCHEZ</t>
   </si>
   <si>
-    <t>BACILIO</t>
+    <t>PEREZ</t>
   </si>
   <si>
-    <t>COCOTLE</t>
+    <t>VASQUEZ</t>
   </si>
   <si>
-    <t>COLOHUA</t>
+    <t>NATALIA</t>
   </si>
   <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUERRERO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>QUIROGA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>CALCANEO</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>POOT</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAELIS</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>MAR EDITH</t>
-  </si>
-  <si>
-    <t>MELISA</t>
-  </si>
-  <si>
-    <t>JUAN ALONSO</t>
-  </si>
-  <si>
-    <t>CRIZULY AMITHAI</t>
-  </si>
-  <si>
-    <t>ADIEL ALONSO</t>
-  </si>
-  <si>
-    <t>LLUVIA ITZEL</t>
-  </si>
-  <si>
-    <t>EUNICE</t>
-  </si>
-  <si>
-    <t>REYNA IVETT</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>HANNA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>KAROL BALAAM</t>
-  </si>
-  <si>
-    <t>MELANIE YARETZI</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>YASMIN</t>
-  </si>
-  <si>
-    <t>XIMENA ANALY</t>
-  </si>
-  <si>
-    <t>ROSA EVELYN</t>
-  </si>
-  <si>
-    <t>VANIA</t>
-  </si>
-  <si>
-    <t>DARLA AMERICA</t>
-  </si>
-  <si>
-    <t>SAMANTHA BETHANY</t>
-  </si>
-  <si>
-    <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
-    <t>MARIEL BIDEMI</t>
-  </si>
-  <si>
-    <t>CARMEN VANELI</t>
+    <t>DIANA PAOLA</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="AK4">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,7 +1016,7 @@
         <v>7</v>
       </c>
       <c r="AK5">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,7 +1129,7 @@
         <v>7</v>
       </c>
       <c r="AK6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,7 +1242,7 @@
         <v>5</v>
       </c>
       <c r="AK7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1571,7 +1355,7 @@
         <v>5</v>
       </c>
       <c r="AK8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1684,7 +1468,7 @@
         <v>6</v>
       </c>
       <c r="AK9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1797,7 +1581,7 @@
         <v>10</v>
       </c>
       <c r="AK10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1910,7 +1694,7 @@
         <v>6</v>
       </c>
       <c r="AK11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2023,7 +1807,7 @@
         <v>7</v>
       </c>
       <c r="AK12">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2136,7 +1920,7 @@
         <v>7</v>
       </c>
       <c r="AK13">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2249,7 +2033,7 @@
         <v>6</v>
       </c>
       <c r="AK14">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2362,7 +2146,7 @@
         <v>8</v>
       </c>
       <c r="AK15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2475,7 +2259,7 @@
         <v>5</v>
       </c>
       <c r="AK16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2588,7 +2372,7 @@
         <v>6</v>
       </c>
       <c r="AK17">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2701,7 +2485,7 @@
         <v>8</v>
       </c>
       <c r="AK18">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2814,7 +2598,7 @@
         <v>7</v>
       </c>
       <c r="AK19">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2927,7 +2711,7 @@
         <v>7</v>
       </c>
       <c r="AK20">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3040,7 +2824,7 @@
         <v>6</v>
       </c>
       <c r="AK21">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3153,7 +2937,7 @@
         <v>7</v>
       </c>
       <c r="AK22">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3266,7 +3050,7 @@
         <v>8</v>
       </c>
       <c r="AK23">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3379,7 +3163,7 @@
         <v>10</v>
       </c>
       <c r="AK24">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3492,7 +3276,7 @@
         <v>6</v>
       </c>
       <c r="AK25">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3605,7 +3389,7 @@
         <v>6</v>
       </c>
       <c r="AK26">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -3718,7 +3502,7 @@
         <v>6</v>
       </c>
       <c r="AK27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -3831,7 +3615,7 @@
         <v>6</v>
       </c>
       <c r="AK28">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -3944,7 +3728,7 @@
         <v>6</v>
       </c>
       <c r="AK29">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -4057,7 +3841,7 @@
         <v>8</v>
       </c>
       <c r="AK30">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4170,7 +3954,7 @@
         <v>7</v>
       </c>
       <c r="AK31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4283,7 +4067,7 @@
         <v>9</v>
       </c>
       <c r="AK32">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -4396,7 +4180,7 @@
         <v>8</v>
       </c>
       <c r="AK33">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:37">
@@ -4509,7 +4293,7 @@
         <v>6</v>
       </c>
       <c r="AK34">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:37">
@@ -4622,7 +4406,7 @@
         <v>5</v>
       </c>
       <c r="AK35">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:37">
@@ -4735,7 +4519,7 @@
         <v>5</v>
       </c>
       <c r="AK36">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:37">
@@ -4848,7 +4632,7 @@
         <v>8</v>
       </c>
       <c r="AK37">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:37">
@@ -4961,7 +4745,7 @@
         <v>10</v>
       </c>
       <c r="AK38">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -8174,7 +7958,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -8183,27 +7967,30 @@
         <v>35</v>
       </c>
       <c r="D2">
+        <v>29</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="G2" s="2">
+        <v>17.1</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>35</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -8212,16 +7999,16 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>82.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G3" s="2">
-        <v>17.1</v>
+        <v>14.3</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -8235,7 +8022,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -8244,19 +8031,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>85.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>14.3</v>
+        <v>11.4</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8267,7 +8054,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -8288,7 +8075,7 @@
         <v>11.4</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8299,7 +8086,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -8320,7 +8107,7 @@
         <v>11.4</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8331,7 +8118,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -8352,7 +8139,7 @@
         <v>11.4</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8363,7 +8150,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
@@ -8372,19 +8159,19 @@
         <v>35</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>88.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8395,7 +8182,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
@@ -8416,7 +8203,7 @@
         <v>8.6</v>
       </c>
       <c r="H9">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -8498,7 +8285,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8530,669 +8317,94 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920048</v>
+        <v>23330051920072</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>62</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920049</v>
+        <v>23330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920050</v>
+        <v>23330051920073</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920083</v>
+        <v>23330051920073</v>
       </c>
       <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
         <v>78</v>
       </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920053</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920054</v>
-      </c>
-      <c r="B7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920055</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920056</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920057</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920058</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920246</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920060</v>
-      </c>
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920061</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920062</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920307</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920063</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920064</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920259</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920065</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" t="s">
-        <v>142</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920263</v>
-      </c>
-      <c r="B21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920066</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920067</v>
-      </c>
-      <c r="B23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920068</v>
-      </c>
-      <c r="B24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" t="s">
-        <v>146</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920069</v>
-      </c>
-      <c r="B25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920070</v>
-      </c>
-      <c r="B26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" t="s">
-        <v>148</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920272</v>
-      </c>
-      <c r="B27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920071</v>
-      </c>
-      <c r="B28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920074</v>
-      </c>
-      <c r="B29" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" t="s">
-        <v>123</v>
-      </c>
-      <c r="D29" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>23330051920075</v>
-      </c>
-      <c r="B30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" t="s">
-        <v>105</v>
-      </c>
-      <c r="D30" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ARHM - Estadisticos 20232.xlsx
+++ b/grupos/2ARHM - Estadisticos 20232.xlsx
@@ -852,7 +852,7 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -965,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1078,7 +1078,7 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1191,7 +1191,7 @@
         <v>5</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1304,7 +1304,7 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1417,7 +1417,7 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1530,7 +1530,7 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1643,7 +1643,7 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1670,7 +1670,7 @@
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD11">
         <v>7</v>
@@ -1756,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1869,7 +1869,7 @@
         <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1982,7 +1982,7 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -2208,7 +2208,7 @@
         <v>5</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -2235,7 +2235,7 @@
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD16">
         <v>5</v>
@@ -2321,7 +2321,7 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -2434,7 +2434,7 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -2547,7 +2547,7 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>9</v>
@@ -2660,7 +2660,7 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>6</v>
@@ -2773,7 +2773,7 @@
         <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2886,7 +2886,7 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2999,7 +2999,7 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -3026,7 +3026,7 @@
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD23">
         <v>6</v>
@@ -3112,7 +3112,7 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -3225,7 +3225,7 @@
         <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -3338,7 +3338,7 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>6</v>
@@ -3451,7 +3451,7 @@
         <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>8</v>
@@ -3564,7 +3564,7 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -3677,7 +3677,7 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -3790,7 +3790,7 @@
         <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>10</v>
@@ -3903,7 +3903,7 @@
         <v>10</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>10</v>
@@ -4016,7 +4016,7 @@
         <v>10</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -4129,7 +4129,7 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -4242,7 +4242,7 @@
         <v>5</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>8</v>
@@ -4355,7 +4355,7 @@
         <v>10</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>5</v>
@@ -4382,7 +4382,7 @@
         <v>10</v>
       </c>
       <c r="AC35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD35">
         <v>5</v>
@@ -4468,7 +4468,7 @@
         <v>10</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>5</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>10</v>
@@ -4694,7 +4694,7 @@
         <v>10</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U38">
         <v>10</v>
@@ -5039,7 +5039,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U5">
         <v>93.7</v>
@@ -5469,7 +5469,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -5555,7 +5555,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -5641,7 +5641,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -5727,7 +5727,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -5813,7 +5813,7 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -5985,7 +5985,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U16">
         <v>42.9</v>
@@ -6071,7 +6071,7 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U17">
         <v>87.3</v>
@@ -6157,7 +6157,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -6329,7 +6329,7 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="U20">
         <v>95.2</v>
@@ -6415,7 +6415,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U21">
         <v>73</v>
@@ -6587,7 +6587,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -6759,7 +6759,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -6845,7 +6845,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -7017,7 +7017,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -7103,7 +7103,7 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -7275,7 +7275,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -7361,7 +7361,7 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -7447,7 +7447,7 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U33">
         <v>100</v>
@@ -7533,7 +7533,7 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U34">
         <v>95.2</v>
@@ -7619,7 +7619,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="U35">
         <v>54</v>
@@ -7705,7 +7705,7 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="U36">
         <v>47.6</v>
@@ -7877,7 +7877,7 @@
         <v>100</v>
       </c>
       <c r="T38">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -8235,7 +8235,7 @@
         <v>5.7</v>
       </c>
       <c r="H10">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I10">
         <v>0</v>
